--- a/data/trans_camb/P44-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P44-Clase-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 12,33</t>
+          <t>-5,67; 11,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,96; 45,22</t>
+          <t>27,98; 45,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-27,69; -0,74</t>
+          <t>-27,7; 0,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,86; 30,1</t>
+          <t>5,56; 31,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,1; 5,68</t>
+          <t>-10,67; 5,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,77; 37,1</t>
+          <t>23,37; 37,59</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-33,99; 132,2</t>
+          <t>-30,61; 131,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>126,81; 502,58</t>
+          <t>126,01; 513,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-83,94; 3,56</t>
+          <t>-83,34; 6,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,34; 210,04</t>
+          <t>15,02; 253,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-47,63; 47,18</t>
+          <t>-46,0; 42,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>98,41; 323,15</t>
+          <t>96,08; 308,82</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 17,23</t>
+          <t>0,32; 16,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,98; 34,01</t>
+          <t>18,71; 34,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,66; 2,9</t>
+          <t>-17,02; 2,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,37; 32,85</t>
+          <t>11,78; 32,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 7,95</t>
+          <t>-4,45; 8,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,61; 30,99</t>
+          <t>18,69; 31,33</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 250,14</t>
+          <t>0,19; 228,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>105,63; 463,75</t>
+          <t>111,52; 491,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-88,3; 77,69</t>
+          <t>-88,48; 86,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53,0; 627,29</t>
+          <t>49,03; 535,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,61; 93,79</t>
+          <t>-31,86; 97,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>114,0; 394,27</t>
+          <t>117,58; 391,16</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 5,69</t>
+          <t>-6,14; 5,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25,67; 81,99</t>
+          <t>25,87; 80,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 9,19</t>
+          <t>-8,87; 9,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,8; 32,4</t>
+          <t>14,1; 32,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 4,57</t>
+          <t>-4,92; 5,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,33; 78,23</t>
+          <t>25,01; 76,75</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-43,83; 71,47</t>
+          <t>-40,72; 73,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>217,21; 1214,74</t>
+          <t>217,35; 1686,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-65,04; 182,7</t>
+          <t>-67,31; 169,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>80,65; 625,0</t>
+          <t>93,42; 718,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-41,83; 58,79</t>
+          <t>-36,88; 61,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>223,18; 1192,64</t>
+          <t>223,49; 1065,22</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 5,49</t>
+          <t>-2,68; 4,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,9; 28,06</t>
+          <t>18,47; 27,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 7,28</t>
+          <t>-4,15; 7,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 22,9</t>
+          <t>-2,99; 22,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 4,43</t>
+          <t>-1,87; 4,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,98; 23,68</t>
+          <t>3,66; 23,24</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-23,98; 82,91</t>
+          <t>-25,31; 77,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>168,47; 431,11</t>
+          <t>168,69; 450,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-36,05; 143,66</t>
+          <t>-38,57; 145,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-44,05; 345,53</t>
+          <t>-22,06; 349,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 65,53</t>
+          <t>-19,02; 63,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,23; 319,29</t>
+          <t>36,34; 311,87</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 8,55</t>
+          <t>-0,47; 8,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18,34; 30,69</t>
+          <t>17,76; 29,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 3,99</t>
+          <t>-3,59; 4,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,01; 22,5</t>
+          <t>14,29; 22,73</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 4,75</t>
+          <t>-1,19; 5,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,51; 23,74</t>
+          <t>16,43; 23,59</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 336,89</t>
+          <t>-13,97; 338,07</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>228,47; 1304,92</t>
+          <t>218,84; 1161,69</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-40,3; 69,27</t>
+          <t>-38,18; 88,4</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>138,9; 428,86</t>
+          <t>139,39; 424,93</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-18,9; 91,67</t>
+          <t>-14,86; 98,39</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>183,4; 492,47</t>
+          <t>178,38; 454,15</t>
         </is>
       </c>
     </row>
@@ -1416,27 +1416,27 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>13,75; 58,27</t>
+          <t>13,15; 62,78</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 3,83</t>
+          <t>-1,53; 3,49</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18,57; 25,62</t>
+          <t>18,52; 25,89</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 3,43</t>
+          <t>-1,62; 3,66</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,7; 25,78</t>
+          <t>18,59; 25,87</t>
         </is>
       </c>
     </row>
@@ -1497,22 +1497,22 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-28,47; 100,89</t>
+          <t>-25,21; 86,43</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>276,9; 695,33</t>
+          <t>273,43; 697,79</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-27,29; 86,22</t>
+          <t>-28,52; 95,31</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>280,05; 659,08</t>
+          <t>269,27; 665,22</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 4,72</t>
+          <t>-0,35; 4,67</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>26,2; 57,7</t>
+          <t>26,02; 55,55</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 1,92</t>
+          <t>-1,93; 2,08</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8,65; 23,48</t>
+          <t>11,2; 23,22</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 2,66</t>
+          <t>-0,58; 2,7</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,24; 42,71</t>
+          <t>21,34; 43,61</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 58,02</t>
+          <t>-3,82; 54,67</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>257,64; 666,09</t>
+          <t>258,49; 661,43</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-26,5; 29,21</t>
+          <t>-22,46; 33,5</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>135,95; 348,9</t>
+          <t>144,6; 343,21</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 34,8</t>
+          <t>-6,16; 35,17</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>244,06; 535,99</t>
+          <t>241,9; 535,95</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P44-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P44-Clase-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>36,98</t>
+          <t>36,34</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18,77</t>
+          <t>19,41</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,56</t>
+          <t>30,39</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 11,9</t>
+          <t>-7,33; 12,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,98; 45,15</t>
+          <t>26,14; 44,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-27,7; 0,49</t>
+          <t>-27,1; -1,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,56; 31,41</t>
+          <t>5,45; 31,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 5,06</t>
+          <t>-9,82; 5,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,37; 37,59</t>
+          <t>22,64; 37,29</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>256,26%</t>
+          <t>251,82%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>179,66%</t>
+          <t>178,66%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-30,61; 131,79</t>
+          <t>-35,47; 136,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>126,01; 513,18</t>
+          <t>119,71; 493,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-83,34; 6,95</t>
+          <t>-83,15; -4,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,02; 253,38</t>
+          <t>14,69; 240,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,0; 42,35</t>
+          <t>-45,97; 41,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>96,08; 308,82</t>
+          <t>94,03; 319,19</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>26,55</t>
+          <t>25,11</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22,98</t>
+          <t>22,56</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,25</t>
+          <t>24,19</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 16,22</t>
+          <t>-1,53; 16,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,71; 34,39</t>
+          <t>16,85; 32,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,02; 2,75</t>
+          <t>-19,09; 1,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,78; 32,38</t>
+          <t>10,61; 32,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 8,03</t>
+          <t>-4,56; 8,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,69; 31,33</t>
+          <t>17,17; 30,39</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>239,93%</t>
+          <t>226,92%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>187,86%</t>
+          <t>184,4%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>220,76%</t>
+          <t>211,49%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 228,98</t>
+          <t>-10,78; 237,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>111,52; 491,67</t>
+          <t>97,53; 461,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-88,48; 86,23</t>
+          <t>-90,89; 54,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49,03; 535,86</t>
+          <t>46,54; 605,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,86; 97,34</t>
+          <t>-31,01; 102,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>117,58; 391,16</t>
+          <t>103,53; 395,34</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>60,35</t>
+          <t>27,1</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23,35</t>
+          <t>23,55</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>54,04</t>
+          <t>25,98</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 5,95</t>
+          <t>-5,89; 5,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25,87; 80,13</t>
+          <t>19,42; 34,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 9,05</t>
+          <t>-9,53; 8,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,1; 32,63</t>
+          <t>13,81; 32,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 5,07</t>
+          <t>-5,56; 4,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,01; 76,75</t>
+          <t>19,77; 31,3</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>528,28%</t>
+          <t>237,27%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>253,37%</t>
+          <t>255,56%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>503,78%</t>
+          <t>242,19%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-40,72; 73,29</t>
+          <t>-42,08; 73,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>217,35; 1686,11</t>
+          <t>126,3; 434,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-67,31; 169,74</t>
+          <t>-71,46; 171,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>93,42; 718,84</t>
+          <t>79,55; 661,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-36,88; 61,21</t>
+          <t>-41,26; 58,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>223,49; 1065,22</t>
+          <t>137,2; 398,73</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>23,28</t>
+          <t>23,67</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9,22</t>
+          <t>20,9</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,2</t>
+          <t>22,6</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 4,96</t>
+          <t>-2,42; 5,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,47; 27,72</t>
+          <t>19,43; 28,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 7,09</t>
+          <t>-3,92; 7,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 22,79</t>
+          <t>15,72; 26,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 4,27</t>
+          <t>-1,66; 4,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,66; 23,24</t>
+          <t>18,6; 25,71</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>276,52%</t>
+          <t>281,16%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>116,9%</t>
+          <t>265,13%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>196,13%</t>
+          <t>273,68%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-25,31; 77,7</t>
+          <t>-23,25; 76,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>168,69; 450,19</t>
+          <t>180,9; 460,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-38,57; 145,49</t>
+          <t>-37,99; 156,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-22,06; 349,43</t>
+          <t>127,85; 546,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-19,02; 63,02</t>
+          <t>-18,16; 66,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,34; 311,87</t>
+          <t>181,5; 395,33</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>23,91</t>
+          <t>23,66</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18,67</t>
+          <t>18,89</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,51</t>
+          <t>20,58</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 8,82</t>
+          <t>-0,78; 8,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17,76; 29,53</t>
+          <t>17,57; 30,37</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 4,7</t>
+          <t>-3,82; 4,17</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,29; 22,73</t>
+          <t>14,1; 22,92</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 5,03</t>
+          <t>-1,7; 4,44</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,43; 23,59</t>
+          <t>17,08; 23,98</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>474,62%</t>
+          <t>469,64%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>248,96%</t>
+          <t>251,91%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>308,5%</t>
+          <t>309,54%</t>
         </is>
       </c>
     </row>
@@ -1331,39 +1331,39 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-13,97; 338,07</t>
+          <t>-12,92; 301,54</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>218,84; 1161,69</t>
+          <t>197,03; 1075,88</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-38,18; 88,4</t>
+          <t>-42,12; 73,03</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>139,39; 424,93</t>
+          <t>132,56; 458,72</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-14,86; 98,39</t>
+          <t>-20,36; 87,15</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>178,38; 454,15</t>
+          <t>198,97; 497,29</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>33,92</t>
+          <t>33,6</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22,16</t>
+          <t>22,91</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,36</t>
+          <t>23,07</t>
         </is>
       </c>
     </row>
@@ -1416,27 +1416,27 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>13,15; 62,78</t>
+          <t>11,68; 63,61</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 3,49</t>
+          <t>-1,54; 3,71</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18,52; 25,89</t>
+          <t>19,75; 26,76</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 3,66</t>
+          <t>-1,57; 3,53</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,59; 25,87</t>
+          <t>19,52; 26,62</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>431,39%</t>
+          <t>445,92%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>437,91%</t>
+          <t>451,8%</t>
         </is>
       </c>
     </row>
@@ -1497,22 +1497,22 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-25,21; 86,43</t>
+          <t>-26,82; 90,24</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>273,43; 697,79</t>
+          <t>300,56; 699,64</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-28,52; 95,31</t>
+          <t>-24,7; 96,8</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>269,27; 665,22</t>
+          <t>292,65; 698,75</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>36,46</t>
+          <t>26,85</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>19,08</t>
+          <t>22,87</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,61</t>
+          <t>24,82</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 4,67</t>
+          <t>-0,17; 4,79</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>26,02; 55,55</t>
+          <t>24,05; 29,98</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 2,08</t>
+          <t>-2,01; 2,23</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11,2; 23,22</t>
+          <t>20,76; 25,06</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 2,7</t>
+          <t>-0,46; 2,72</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,34; 43,61</t>
+          <t>23,04; 26,38</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>382,75%</t>
+          <t>281,83%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>255,84%</t>
+          <t>306,69%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>329,09%</t>
+          <t>295,93%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 54,67</t>
+          <t>-1,57; 57,9</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>258,49; 661,43</t>
+          <t>215,62; 378,86</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-22,46; 33,5</t>
+          <t>-23,7; 35,3</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>144,6; 343,21</t>
+          <t>234,78; 402,98</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 35,17</t>
+          <t>-4,37; 35,91</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>241,9; 535,95</t>
+          <t>243,89; 346,1</t>
         </is>
       </c>
     </row>
